--- a/Capítulo02/Capítulo02/FORMATACAO DE DATAS.xlsx
+++ b/Capítulo02/Capítulo02/FORMATACAO DE DATAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Livro Excel 2019\Avançado\Excel 2019\Planilhas\Capítulo2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7747010-E47A-44CA-898A-42A8707C5310}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E7747010-E47A-44CA-898A-42A8707C5310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3535B2DC-B704-40FA-B81B-0B8EEC30932F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="165" formatCode="dd"/>
+    <numFmt numFmtId="168" formatCode="dddd"/>
+    <numFmt numFmtId="169" formatCode="mmmm"/>
+    <numFmt numFmtId="170" formatCode="dddd/mmmm/yyyy"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -101,11 +107,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -130,9 +151,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -170,9 +191,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -205,26 +226,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -257,26 +261,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,7 +441,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
@@ -482,16 +469,16 @@
       <c r="A2" s="1">
         <v>40557</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>40557</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="5">
         <v>40557</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="6">
         <v>40557</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="7">
         <v>40557</v>
       </c>
     </row>
@@ -499,221 +486,221 @@
       <c r="A3" s="1">
         <v>40565</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
+        <v>40558</v>
+      </c>
+      <c r="C3" s="5">
         <v>40565</v>
       </c>
-      <c r="C3" s="1">
-        <v>40565</v>
-      </c>
-      <c r="D3" s="1">
-        <v>40565</v>
-      </c>
-      <c r="E3" s="1">
-        <v>40565</v>
+      <c r="D3" s="6">
+        <v>40558</v>
+      </c>
+      <c r="E3" s="7">
+        <v>40558</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>40574</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
+        <v>40559</v>
+      </c>
+      <c r="C4" s="5">
         <v>40574</v>
       </c>
-      <c r="C4" s="1">
-        <v>40574</v>
-      </c>
-      <c r="D4" s="1">
-        <v>40574</v>
-      </c>
-      <c r="E4" s="1">
-        <v>40574</v>
+      <c r="D4" s="6">
+        <v>40559</v>
+      </c>
+      <c r="E4" s="7">
+        <v>40559</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>40584</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
+        <v>40560</v>
+      </c>
+      <c r="C5" s="5">
         <v>40584</v>
       </c>
-      <c r="C5" s="1">
-        <v>40584</v>
-      </c>
-      <c r="D5" s="1">
-        <v>40584</v>
-      </c>
-      <c r="E5" s="1">
-        <v>40584</v>
+      <c r="D5" s="6">
+        <v>40560</v>
+      </c>
+      <c r="E5" s="7">
+        <v>40560</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>40663</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
+        <v>40561</v>
+      </c>
+      <c r="C6" s="5">
         <v>40663</v>
       </c>
-      <c r="C6" s="1">
-        <v>40663</v>
-      </c>
-      <c r="D6" s="1">
-        <v>40663</v>
-      </c>
-      <c r="E6" s="1">
-        <v>40663</v>
+      <c r="D6" s="6">
+        <v>40561</v>
+      </c>
+      <c r="E6" s="7">
+        <v>40561</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>40674</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
+        <v>40562</v>
+      </c>
+      <c r="C7" s="5">
         <v>40674</v>
       </c>
-      <c r="C7" s="1">
-        <v>40674</v>
-      </c>
-      <c r="D7" s="1">
-        <v>40674</v>
-      </c>
-      <c r="E7" s="1">
-        <v>40674</v>
+      <c r="D7" s="6">
+        <v>40562</v>
+      </c>
+      <c r="E7" s="7">
+        <v>40562</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>40720</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="3">
+        <v>40563</v>
+      </c>
+      <c r="C8" s="5">
         <v>40720</v>
       </c>
-      <c r="C8" s="1">
-        <v>40720</v>
-      </c>
-      <c r="D8" s="1">
-        <v>40720</v>
-      </c>
-      <c r="E8" s="1">
-        <v>40720</v>
+      <c r="D8" s="6">
+        <v>40563</v>
+      </c>
+      <c r="E8" s="7">
+        <v>40563</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>40724</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
+        <v>40564</v>
+      </c>
+      <c r="C9" s="5">
         <v>40724</v>
       </c>
-      <c r="C9" s="1">
-        <v>40724</v>
-      </c>
-      <c r="D9" s="1">
-        <v>40724</v>
-      </c>
-      <c r="E9" s="1">
-        <v>40724</v>
+      <c r="D9" s="6">
+        <v>40564</v>
+      </c>
+      <c r="E9" s="7">
+        <v>40564</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>40770</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
+        <v>40565</v>
+      </c>
+      <c r="C10" s="5">
         <v>40770</v>
       </c>
-      <c r="C10" s="1">
-        <v>40770</v>
-      </c>
-      <c r="D10" s="1">
-        <v>40770</v>
-      </c>
-      <c r="E10" s="1">
-        <v>40770</v>
+      <c r="D10" s="6">
+        <v>40565</v>
+      </c>
+      <c r="E10" s="7">
+        <v>40565</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>40796</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
+        <v>40566</v>
+      </c>
+      <c r="C11" s="5">
         <v>40796</v>
       </c>
-      <c r="C11" s="1">
-        <v>40796</v>
-      </c>
-      <c r="D11" s="1">
-        <v>40796</v>
-      </c>
-      <c r="E11" s="1">
-        <v>40796</v>
+      <c r="D11" s="6">
+        <v>40566</v>
+      </c>
+      <c r="E11" s="7">
+        <v>40566</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>40809</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
+        <v>40567</v>
+      </c>
+      <c r="C12" s="5">
         <v>40809</v>
       </c>
-      <c r="C12" s="1">
-        <v>40809</v>
-      </c>
-      <c r="D12" s="1">
-        <v>40809</v>
-      </c>
-      <c r="E12" s="1">
-        <v>40809</v>
+      <c r="D12" s="6">
+        <v>40567</v>
+      </c>
+      <c r="E12" s="7">
+        <v>40567</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>40828</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
+        <v>40568</v>
+      </c>
+      <c r="C13" s="5">
         <v>40828</v>
       </c>
-      <c r="C13" s="1">
-        <v>40828</v>
-      </c>
-      <c r="D13" s="1">
-        <v>40828</v>
-      </c>
-      <c r="E13" s="1">
-        <v>40828</v>
+      <c r="D13" s="6">
+        <v>40568</v>
+      </c>
+      <c r="E13" s="7">
+        <v>40568</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>40853</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
+        <v>40569</v>
+      </c>
+      <c r="C14" s="5">
         <v>40853</v>
       </c>
-      <c r="C14" s="1">
-        <v>40853</v>
-      </c>
-      <c r="D14" s="1">
-        <v>40853</v>
-      </c>
-      <c r="E14" s="1">
-        <v>40853</v>
+      <c r="D14" s="6">
+        <v>40569</v>
+      </c>
+      <c r="E14" s="7">
+        <v>40569</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>40901</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
+        <v>40570</v>
+      </c>
+      <c r="C15" s="5">
         <v>40901</v>
       </c>
-      <c r="C15" s="1">
-        <v>40901</v>
-      </c>
-      <c r="D15" s="1">
-        <v>40901</v>
-      </c>
-      <c r="E15" s="1">
-        <v>40901</v>
+      <c r="D15" s="6">
+        <v>40570</v>
+      </c>
+      <c r="E15" s="7">
+        <v>40570</v>
       </c>
     </row>
   </sheetData>
@@ -744,6 +731,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -857,29 +859,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E824DE20-D1D9-4EAF-A616-080B6774D133}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3541448-459F-419A-9901-3F5640BB60D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E16AAC7E-7444-4F3F-9B6C-34B6F0EEF96E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E16AAC7E-7444-4F3F-9B6C-34B6F0EEF96E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3541448-459F-419A-9901-3F5640BB60D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E824DE20-D1D9-4EAF-A616-080B6774D133}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Capítulo02/Capítulo02/FORMATACAO DE DATAS.xlsx
+++ b/Capítulo02/Capítulo02/FORMATACAO DE DATAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E7747010-E47A-44CA-898A-42A8707C5310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3535B2DC-B704-40FA-B81B-0B8EEC30932F}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{E7747010-E47A-44CA-898A-42A8707C5310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47243F33-5CDF-4002-B5B5-38ACE2AFD487}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,20 @@
     <sheet name="Plan2" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -44,10 +57,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="dd"/>
-    <numFmt numFmtId="168" formatCode="dddd"/>
-    <numFmt numFmtId="169" formatCode="mmmm"/>
-    <numFmt numFmtId="170" formatCode="dddd/mmmm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dddd"/>
+    <numFmt numFmtId="166" formatCode="mmmm"/>
+    <numFmt numFmtId="170" formatCode="[$-416]d;@"/>
+    <numFmt numFmtId="171" formatCode="dd/mmmm/yyyy"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -113,21 +126,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,8 +447,8 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
@@ -469,14 +476,14 @@
       <c r="A2" s="1">
         <v>40557</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>40557</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>40557</v>
       </c>
-      <c r="D2" s="6">
-        <v>40557</v>
+      <c r="D2" s="5">
+        <v>40558</v>
       </c>
       <c r="E2" s="7">
         <v>40557</v>
@@ -486,221 +493,221 @@
       <c r="A3" s="1">
         <v>40565</v>
       </c>
-      <c r="B3" s="3">
-        <v>40558</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="6">
         <v>40565</v>
       </c>
-      <c r="D3" s="6">
-        <v>40558</v>
+      <c r="C3" s="4">
+        <v>40565</v>
+      </c>
+      <c r="D3" s="5">
+        <v>40565</v>
       </c>
       <c r="E3" s="7">
-        <v>40558</v>
+        <v>40565</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>40574</v>
       </c>
-      <c r="B4" s="3">
-        <v>40559</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="6">
         <v>40574</v>
       </c>
-      <c r="D4" s="6">
-        <v>40559</v>
+      <c r="C4" s="4">
+        <v>40574</v>
+      </c>
+      <c r="D4" s="5">
+        <v>40574</v>
       </c>
       <c r="E4" s="7">
-        <v>40559</v>
+        <v>40574</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>40584</v>
       </c>
-      <c r="B5" s="3">
-        <v>40560</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="6">
         <v>40584</v>
       </c>
-      <c r="D5" s="6">
-        <v>40560</v>
+      <c r="C5" s="4">
+        <v>40584</v>
+      </c>
+      <c r="D5" s="5">
+        <v>40584</v>
       </c>
       <c r="E5" s="7">
-        <v>40560</v>
+        <v>40584</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>40663</v>
       </c>
-      <c r="B6" s="3">
-        <v>40561</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="6">
         <v>40663</v>
       </c>
-      <c r="D6" s="6">
-        <v>40561</v>
+      <c r="C6" s="4">
+        <v>40663</v>
+      </c>
+      <c r="D6" s="5">
+        <v>40663</v>
       </c>
       <c r="E6" s="7">
-        <v>40561</v>
+        <v>40663</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>40674</v>
       </c>
-      <c r="B7" s="3">
-        <v>40562</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="6">
         <v>40674</v>
       </c>
-      <c r="D7" s="6">
-        <v>40562</v>
+      <c r="C7" s="4">
+        <v>40674</v>
+      </c>
+      <c r="D7" s="5">
+        <v>40674</v>
       </c>
       <c r="E7" s="7">
-        <v>40562</v>
+        <v>40674</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>40720</v>
       </c>
-      <c r="B8" s="3">
-        <v>40563</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="6">
         <v>40720</v>
       </c>
-      <c r="D8" s="6">
-        <v>40563</v>
+      <c r="C8" s="4">
+        <v>40720</v>
+      </c>
+      <c r="D8" s="5">
+        <v>40720</v>
       </c>
       <c r="E8" s="7">
-        <v>40563</v>
+        <v>40720</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>40724</v>
       </c>
-      <c r="B9" s="3">
-        <v>40564</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="6">
         <v>40724</v>
       </c>
-      <c r="D9" s="6">
-        <v>40564</v>
+      <c r="C9" s="4">
+        <v>40724</v>
+      </c>
+      <c r="D9" s="5">
+        <v>40724</v>
       </c>
       <c r="E9" s="7">
-        <v>40564</v>
+        <v>40724</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>40770</v>
       </c>
-      <c r="B10" s="3">
-        <v>40565</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="6">
         <v>40770</v>
       </c>
-      <c r="D10" s="6">
-        <v>40565</v>
+      <c r="C10" s="4">
+        <v>40770</v>
+      </c>
+      <c r="D10" s="5">
+        <v>40770</v>
       </c>
       <c r="E10" s="7">
-        <v>40565</v>
+        <v>40770</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>40796</v>
       </c>
-      <c r="B11" s="3">
-        <v>40566</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="6">
         <v>40796</v>
       </c>
-      <c r="D11" s="6">
-        <v>40566</v>
+      <c r="C11" s="4">
+        <v>40796</v>
+      </c>
+      <c r="D11" s="5">
+        <v>40796</v>
       </c>
       <c r="E11" s="7">
-        <v>40566</v>
+        <v>40796</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>40809</v>
       </c>
-      <c r="B12" s="3">
-        <v>40567</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="6">
         <v>40809</v>
       </c>
-      <c r="D12" s="6">
-        <v>40567</v>
+      <c r="C12" s="4">
+        <v>40809</v>
+      </c>
+      <c r="D12" s="5">
+        <v>40809</v>
       </c>
       <c r="E12" s="7">
-        <v>40567</v>
+        <v>40809</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>40828</v>
       </c>
-      <c r="B13" s="3">
-        <v>40568</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="6">
         <v>40828</v>
       </c>
-      <c r="D13" s="6">
-        <v>40568</v>
+      <c r="C13" s="4">
+        <v>40828</v>
+      </c>
+      <c r="D13" s="5">
+        <v>40828</v>
       </c>
       <c r="E13" s="7">
-        <v>40568</v>
+        <v>40828</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>40853</v>
       </c>
-      <c r="B14" s="3">
-        <v>40569</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="6">
         <v>40853</v>
       </c>
-      <c r="D14" s="6">
-        <v>40569</v>
+      <c r="C14" s="4">
+        <v>40853</v>
+      </c>
+      <c r="D14" s="5">
+        <v>40853</v>
       </c>
       <c r="E14" s="7">
-        <v>40569</v>
+        <v>40853</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>40901</v>
       </c>
-      <c r="B15" s="3">
-        <v>40570</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="6">
         <v>40901</v>
       </c>
-      <c r="D15" s="6">
-        <v>40570</v>
+      <c r="C15" s="4">
+        <v>40901</v>
+      </c>
+      <c r="D15" s="5">
+        <v>40901</v>
       </c>
       <c r="E15" s="7">
-        <v>40570</v>
+        <v>40901</v>
       </c>
     </row>
   </sheetData>
@@ -731,21 +738,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -859,24 +851,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3541448-459F-419A-9901-3F5640BB60D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E16AAC7E-7444-4F3F-9B6C-34B6F0EEF96E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E824DE20-D1D9-4EAF-A616-080B6774D133}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -890,4 +880,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E16AAC7E-7444-4F3F-9B6C-34B6F0EEF96E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3541448-459F-419A-9901-3F5640BB60D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>